--- a/Data/EC/NIT-9004250174.xlsx
+++ b/Data/EC/NIT-9004250174.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\NIYARAKY\MACROS AJUSTADAS\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ysarm\OneDrive\Desktop\MACROS\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C6960350-40C6-48B1-9688-343E4EBEB259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2736201B-07E8-4586-B4D2-FBE13C037337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{25E45DC4-80FF-48BD-835E-53164EEF2C2D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{037F9705-D541-4237-9F28-E8F268419667}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="84">
   <si>
     <t>Tipo Doc Trabajador</t>
   </si>
@@ -71,172 +71,190 @@
     <t>MANUELA HERRERA DIAZ</t>
   </si>
   <si>
+    <t>2602</t>
+  </si>
+  <si>
+    <t>2601</t>
+  </si>
+  <si>
+    <t>2512</t>
+  </si>
+  <si>
+    <t>2511</t>
+  </si>
+  <si>
+    <t>2510</t>
+  </si>
+  <si>
+    <t>2509</t>
+  </si>
+  <si>
+    <t>2508</t>
+  </si>
+  <si>
+    <t>2507</t>
+  </si>
+  <si>
+    <t>2506</t>
+  </si>
+  <si>
+    <t>2505</t>
+  </si>
+  <si>
+    <t>2504</t>
+  </si>
+  <si>
+    <t>2503</t>
+  </si>
+  <si>
+    <t>2502</t>
+  </si>
+  <si>
+    <t>2501</t>
+  </si>
+  <si>
+    <t>2412</t>
+  </si>
+  <si>
+    <t>2411</t>
+  </si>
+  <si>
+    <t>2410</t>
+  </si>
+  <si>
+    <t>2409</t>
+  </si>
+  <si>
+    <t>2408</t>
+  </si>
+  <si>
+    <t>2407</t>
+  </si>
+  <si>
+    <t>2406</t>
+  </si>
+  <si>
+    <t>2405</t>
+  </si>
+  <si>
+    <t>2404</t>
+  </si>
+  <si>
+    <t>2403</t>
+  </si>
+  <si>
+    <t>2402</t>
+  </si>
+  <si>
+    <t>2401</t>
+  </si>
+  <si>
+    <t>2312</t>
+  </si>
+  <si>
+    <t>2311</t>
+  </si>
+  <si>
+    <t>2310</t>
+  </si>
+  <si>
+    <t>2309</t>
+  </si>
+  <si>
+    <t>2308</t>
+  </si>
+  <si>
+    <t>2307</t>
+  </si>
+  <si>
+    <t>2306</t>
+  </si>
+  <si>
+    <t>2305</t>
+  </si>
+  <si>
+    <t>2304</t>
+  </si>
+  <si>
+    <t>2303</t>
+  </si>
+  <si>
+    <t>2302</t>
+  </si>
+  <si>
+    <t>2301</t>
+  </si>
+  <si>
+    <t>2212</t>
+  </si>
+  <si>
+    <t>2211</t>
+  </si>
+  <si>
+    <t>2210</t>
+  </si>
+  <si>
+    <t>2209</t>
+  </si>
+  <si>
+    <t>2208</t>
+  </si>
+  <si>
+    <t>2207</t>
+  </si>
+  <si>
+    <t>2206</t>
+  </si>
+  <si>
+    <t>2205</t>
+  </si>
+  <si>
+    <t>2204</t>
+  </si>
+  <si>
+    <t>2203</t>
+  </si>
+  <si>
+    <t>2202</t>
+  </si>
+  <si>
+    <t>2201</t>
+  </si>
+  <si>
+    <t>2112</t>
+  </si>
+  <si>
+    <t>2111</t>
+  </si>
+  <si>
+    <t>2110</t>
+  </si>
+  <si>
+    <t>2109</t>
+  </si>
+  <si>
+    <t>2108</t>
+  </si>
+  <si>
+    <t>2107</t>
+  </si>
+  <si>
+    <t>2106</t>
+  </si>
+  <si>
+    <t>2105</t>
+  </si>
+  <si>
+    <t>2104</t>
+  </si>
+  <si>
+    <t>2103</t>
+  </si>
+  <si>
+    <t>2102</t>
+  </si>
+  <si>
     <t>2101</t>
-  </si>
-  <si>
-    <t>2102</t>
-  </si>
-  <si>
-    <t>2103</t>
-  </si>
-  <si>
-    <t>2104</t>
-  </si>
-  <si>
-    <t>2105</t>
-  </si>
-  <si>
-    <t>2106</t>
-  </si>
-  <si>
-    <t>2107</t>
-  </si>
-  <si>
-    <t>2108</t>
-  </si>
-  <si>
-    <t>2109</t>
-  </si>
-  <si>
-    <t>2110</t>
-  </si>
-  <si>
-    <t>2111</t>
-  </si>
-  <si>
-    <t>2112</t>
-  </si>
-  <si>
-    <t>2201</t>
-  </si>
-  <si>
-    <t>2202</t>
-  </si>
-  <si>
-    <t>2203</t>
-  </si>
-  <si>
-    <t>2204</t>
-  </si>
-  <si>
-    <t>2205</t>
-  </si>
-  <si>
-    <t>2206</t>
-  </si>
-  <si>
-    <t>2207</t>
-  </si>
-  <si>
-    <t>2208</t>
-  </si>
-  <si>
-    <t>2209</t>
-  </si>
-  <si>
-    <t>2210</t>
-  </si>
-  <si>
-    <t>2211</t>
-  </si>
-  <si>
-    <t>2212</t>
-  </si>
-  <si>
-    <t>2301</t>
-  </si>
-  <si>
-    <t>2302</t>
-  </si>
-  <si>
-    <t>2303</t>
-  </si>
-  <si>
-    <t>2304</t>
-  </si>
-  <si>
-    <t>2305</t>
-  </si>
-  <si>
-    <t>2306</t>
-  </si>
-  <si>
-    <t>2307</t>
-  </si>
-  <si>
-    <t>2308</t>
-  </si>
-  <si>
-    <t>2309</t>
-  </si>
-  <si>
-    <t>2310</t>
-  </si>
-  <si>
-    <t>2311</t>
-  </si>
-  <si>
-    <t>2312</t>
-  </si>
-  <si>
-    <t>2401</t>
-  </si>
-  <si>
-    <t>2402</t>
-  </si>
-  <si>
-    <t>2403</t>
-  </si>
-  <si>
-    <t>2404</t>
-  </si>
-  <si>
-    <t>2405</t>
-  </si>
-  <si>
-    <t>2406</t>
-  </si>
-  <si>
-    <t>2407</t>
-  </si>
-  <si>
-    <t>2408</t>
-  </si>
-  <si>
-    <t>2409</t>
-  </si>
-  <si>
-    <t>2410</t>
-  </si>
-  <si>
-    <t>2411</t>
-  </si>
-  <si>
-    <t>2412</t>
-  </si>
-  <si>
-    <t>2501</t>
-  </si>
-  <si>
-    <t>2502</t>
-  </si>
-  <si>
-    <t>2503</t>
-  </si>
-  <si>
-    <t>2504</t>
-  </si>
-  <si>
-    <t>2505</t>
-  </si>
-  <si>
-    <t>2506</t>
-  </si>
-  <si>
-    <t>2507</t>
-  </si>
-  <si>
-    <t>2508</t>
   </si>
   <si>
     <t>ESTADO DE CUENTA</t>
@@ -335,159 +353,9 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right/>
       <top style="thin">
         <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
       </top>
       <bottom style="thin">
         <color indexed="64"/>
@@ -505,6 +373,156 @@
         <color indexed="64"/>
       </top>
       <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -550,23 +568,23 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -594,10 +612,10 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -635,22 +653,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>667900</xdr:colOff>
+      <xdr:colOff>717113</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>62300</xdr:rowOff>
+      <xdr:rowOff>75000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>430650</xdr:colOff>
+      <xdr:colOff>435413</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>121850</xdr:rowOff>
+      <xdr:rowOff>115500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC5A4051-61AB-609B-A8A7-ADE6DCCF2DCF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A805F0D9-2CB6-9D81-7E49-D18EF2B17FF8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -672,7 +690,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="921900" y="246450"/>
+          <a:off x="964763" y="265500"/>
           <a:ext cx="975600" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1001,27 +1019,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8EF7CA7-B242-4DE4-B5A6-00F58F466832}">
-  <dimension ref="B2:J77"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC9BD55E-2BB3-4A88-A3A5-F0000254AAB5}">
+  <dimension ref="B2:J83"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.6328125" customWidth="1"/>
-    <col min="2" max="2" width="18.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.36328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.08984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="28"/>
       <c r="D2" s="29" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E2" s="29"/>
       <c r="F2" s="29"/>
@@ -1030,7 +1048,7 @@
       <c r="I2" s="29"/>
       <c r="J2" s="29"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="28"/>
       <c r="D3" s="30"/>
@@ -1041,7 +1059,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="28"/>
       <c r="D4" s="30"/>
@@ -1052,7 +1070,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="28"/>
       <c r="D5" s="31"/>
@@ -1063,10 +1081,10 @@
       <c r="I5" s="31"/>
       <c r="J5" s="31"/>
     </row>
-    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="27"/>
@@ -1079,8 +1097,8 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1095,15 +1113,15 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="27"/>
       <c r="E11" s="7">
-        <v>1966272</v>
+        <v>2176944</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
@@ -1111,27 +1129,27 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C13" s="5">
         <v>1</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="8" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="F13" s="5">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
@@ -1151,16 +1169,16 @@
         <v>5</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.35">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>8</v>
       </c>
@@ -1183,7 +1201,7 @@
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>8</v>
       </c>
@@ -1206,7 +1224,7 @@
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
@@ -1229,7 +1247,7 @@
       <c r="I18" s="19"/>
       <c r="J18" s="20"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
         <v>8</v>
       </c>
@@ -1252,7 +1270,7 @@
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
         <v>8</v>
       </c>
@@ -1275,7 +1293,7 @@
       <c r="I20" s="19"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
         <v>8</v>
       </c>
@@ -1298,7 +1316,7 @@
       <c r="I21" s="19"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
         <v>8</v>
       </c>
@@ -1321,7 +1339,7 @@
       <c r="I22" s="19"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
         <v>8</v>
       </c>
@@ -1344,7 +1362,7 @@
       <c r="I23" s="19"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
         <v>8</v>
       </c>
@@ -1367,7 +1385,7 @@
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
         <v>8</v>
       </c>
@@ -1390,7 +1408,7 @@
       <c r="I25" s="19"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>8</v>
       </c>
@@ -1413,7 +1431,7 @@
       <c r="I26" s="19"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
         <v>8</v>
       </c>
@@ -1436,7 +1454,7 @@
       <c r="I27" s="19"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>8</v>
       </c>
@@ -1459,7 +1477,7 @@
       <c r="I28" s="19"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
         <v>8</v>
       </c>
@@ -1482,7 +1500,7 @@
       <c r="I29" s="19"/>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
         <v>8</v>
       </c>
@@ -1505,7 +1523,7 @@
       <c r="I30" s="19"/>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
         <v>8</v>
       </c>
@@ -1528,7 +1546,7 @@
       <c r="I31" s="19"/>
       <c r="J31" s="20"/>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
         <v>8</v>
       </c>
@@ -1551,7 +1569,7 @@
       <c r="I32" s="19"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
         <v>8</v>
       </c>
@@ -1574,7 +1592,7 @@
       <c r="I33" s="19"/>
       <c r="J33" s="20"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
         <v>8</v>
       </c>
@@ -1597,7 +1615,7 @@
       <c r="I34" s="19"/>
       <c r="J34" s="20"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
         <v>8</v>
       </c>
@@ -1620,7 +1638,7 @@
       <c r="I35" s="19"/>
       <c r="J35" s="20"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
         <v>8</v>
       </c>
@@ -1643,7 +1661,7 @@
       <c r="I36" s="19"/>
       <c r="J36" s="20"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
         <v>8</v>
       </c>
@@ -1666,7 +1684,7 @@
       <c r="I37" s="19"/>
       <c r="J37" s="20"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
@@ -1689,7 +1707,7 @@
       <c r="I38" s="19"/>
       <c r="J38" s="20"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
         <v>8</v>
       </c>
@@ -1712,7 +1730,7 @@
       <c r="I39" s="19"/>
       <c r="J39" s="20"/>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
         <v>8</v>
       </c>
@@ -1735,7 +1753,7 @@
       <c r="I40" s="19"/>
       <c r="J40" s="20"/>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
         <v>8</v>
       </c>
@@ -1758,7 +1776,7 @@
       <c r="I41" s="19"/>
       <c r="J41" s="20"/>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="15" t="s">
         <v>8</v>
       </c>
@@ -1781,7 +1799,7 @@
       <c r="I42" s="19"/>
       <c r="J42" s="20"/>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="15" t="s">
         <v>8</v>
       </c>
@@ -1804,7 +1822,7 @@
       <c r="I43" s="19"/>
       <c r="J43" s="20"/>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="15" t="s">
         <v>8</v>
       </c>
@@ -1827,7 +1845,7 @@
       <c r="I44" s="19"/>
       <c r="J44" s="20"/>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="15" t="s">
         <v>8</v>
       </c>
@@ -1850,7 +1868,7 @@
       <c r="I45" s="19"/>
       <c r="J45" s="20"/>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="15" t="s">
         <v>8</v>
       </c>
@@ -1873,7 +1891,7 @@
       <c r="I46" s="19"/>
       <c r="J46" s="20"/>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="15" t="s">
         <v>8</v>
       </c>
@@ -1896,7 +1914,7 @@
       <c r="I47" s="19"/>
       <c r="J47" s="20"/>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" s="15" t="s">
         <v>8</v>
       </c>
@@ -1919,7 +1937,7 @@
       <c r="I48" s="19"/>
       <c r="J48" s="20"/>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="15" t="s">
         <v>8</v>
       </c>
@@ -1942,7 +1960,7 @@
       <c r="I49" s="19"/>
       <c r="J49" s="20"/>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" s="15" t="s">
         <v>8</v>
       </c>
@@ -1965,7 +1983,7 @@
       <c r="I50" s="19"/>
       <c r="J50" s="20"/>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" s="15" t="s">
         <v>8</v>
       </c>
@@ -1988,7 +2006,7 @@
       <c r="I51" s="19"/>
       <c r="J51" s="20"/>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
         <v>8</v>
       </c>
@@ -2011,7 +2029,7 @@
       <c r="I52" s="19"/>
       <c r="J52" s="20"/>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53" s="15" t="s">
         <v>8</v>
       </c>
@@ -2034,7 +2052,7 @@
       <c r="I53" s="19"/>
       <c r="J53" s="20"/>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" s="15" t="s">
         <v>8</v>
       </c>
@@ -2057,7 +2075,7 @@
       <c r="I54" s="19"/>
       <c r="J54" s="20"/>
     </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55" s="15" t="s">
         <v>8</v>
       </c>
@@ -2080,7 +2098,7 @@
       <c r="I55" s="19"/>
       <c r="J55" s="20"/>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B56" s="15" t="s">
         <v>8</v>
       </c>
@@ -2103,7 +2121,7 @@
       <c r="I56" s="19"/>
       <c r="J56" s="20"/>
     </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57" s="15" t="s">
         <v>8</v>
       </c>
@@ -2126,7 +2144,7 @@
       <c r="I57" s="19"/>
       <c r="J57" s="20"/>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B58" s="15" t="s">
         <v>8</v>
       </c>
@@ -2149,7 +2167,7 @@
       <c r="I58" s="19"/>
       <c r="J58" s="20"/>
     </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B59" s="15" t="s">
         <v>8</v>
       </c>
@@ -2172,7 +2190,7 @@
       <c r="I59" s="19"/>
       <c r="J59" s="20"/>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B60" s="15" t="s">
         <v>8</v>
       </c>
@@ -2195,7 +2213,7 @@
       <c r="I60" s="19"/>
       <c r="J60" s="20"/>
     </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B61" s="15" t="s">
         <v>8</v>
       </c>
@@ -2218,7 +2236,7 @@
       <c r="I61" s="19"/>
       <c r="J61" s="20"/>
     </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B62" s="15" t="s">
         <v>8</v>
       </c>
@@ -2241,7 +2259,7 @@
       <c r="I62" s="19"/>
       <c r="J62" s="20"/>
     </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B63" s="15" t="s">
         <v>8</v>
       </c>
@@ -2264,7 +2282,7 @@
       <c r="I63" s="19"/>
       <c r="J63" s="20"/>
     </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64" s="15" t="s">
         <v>8</v>
       </c>
@@ -2287,7 +2305,7 @@
       <c r="I64" s="19"/>
       <c r="J64" s="20"/>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B65" s="15" t="s">
         <v>8</v>
       </c>
@@ -2310,7 +2328,7 @@
       <c r="I65" s="19"/>
       <c r="J65" s="20"/>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B66" s="15" t="s">
         <v>8</v>
       </c>
@@ -2333,7 +2351,7 @@
       <c r="I66" s="19"/>
       <c r="J66" s="20"/>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67" s="15" t="s">
         <v>8</v>
       </c>
@@ -2356,7 +2374,7 @@
       <c r="I67" s="19"/>
       <c r="J67" s="20"/>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68" s="15" t="s">
         <v>8</v>
       </c>
@@ -2379,7 +2397,7 @@
       <c r="I68" s="19"/>
       <c r="J68" s="20"/>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B69" s="15" t="s">
         <v>8</v>
       </c>
@@ -2402,7 +2420,7 @@
       <c r="I69" s="19"/>
       <c r="J69" s="20"/>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B70" s="15" t="s">
         <v>8</v>
       </c>
@@ -2425,57 +2443,195 @@
       <c r="I70" s="19"/>
       <c r="J70" s="20"/>
     </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B71" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="C71" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D71" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="E71" s="22" t="s">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B71" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C71" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D71" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E71" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="F71" s="24">
-        <v>35112</v>
-      </c>
-      <c r="G71" s="24">
-        <v>877803</v>
-      </c>
-      <c r="H71" s="25"/>
-      <c r="I71" s="25"/>
-      <c r="J71" s="26"/>
-    </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B76" s="32" t="s">
-        <v>76</v>
-      </c>
-      <c r="C76" s="32"/>
-      <c r="H76" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="I76" s="1"/>
-      <c r="J76" s="1"/>
-    </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B77" s="32" t="s">
-        <v>75</v>
-      </c>
-      <c r="C77" s="32"/>
-      <c r="H77" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="I77" s="1"/>
-      <c r="J77" s="1"/>
+      <c r="F71" s="18">
+        <v>35112</v>
+      </c>
+      <c r="G71" s="18">
+        <v>877803</v>
+      </c>
+      <c r="H71" s="19"/>
+      <c r="I71" s="19"/>
+      <c r="J71" s="20"/>
+    </row>
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B72" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C72" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D72" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E72" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="F72" s="18">
+        <v>35112</v>
+      </c>
+      <c r="G72" s="18">
+        <v>877803</v>
+      </c>
+      <c r="H72" s="19"/>
+      <c r="I72" s="19"/>
+      <c r="J72" s="20"/>
+    </row>
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B73" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C73" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D73" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E73" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="F73" s="18">
+        <v>35112</v>
+      </c>
+      <c r="G73" s="18">
+        <v>877803</v>
+      </c>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="20"/>
+    </row>
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B74" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C74" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D74" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E74" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="F74" s="18">
+        <v>35112</v>
+      </c>
+      <c r="G74" s="18">
+        <v>877803</v>
+      </c>
+      <c r="H74" s="19"/>
+      <c r="I74" s="19"/>
+      <c r="J74" s="20"/>
+    </row>
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B75" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C75" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D75" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E75" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="F75" s="18">
+        <v>35112</v>
+      </c>
+      <c r="G75" s="18">
+        <v>877803</v>
+      </c>
+      <c r="H75" s="19"/>
+      <c r="I75" s="19"/>
+      <c r="J75" s="20"/>
+    </row>
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B76" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C76" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D76" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E76" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="F76" s="18">
+        <v>35112</v>
+      </c>
+      <c r="G76" s="18">
+        <v>877803</v>
+      </c>
+      <c r="H76" s="19"/>
+      <c r="I76" s="19"/>
+      <c r="J76" s="20"/>
+    </row>
+    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B77" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C77" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="D77" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="E77" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="F77" s="24">
+        <v>35112</v>
+      </c>
+      <c r="G77" s="24">
+        <v>877803</v>
+      </c>
+      <c r="H77" s="25"/>
+      <c r="I77" s="25"/>
+      <c r="J77" s="26"/>
+    </row>
+    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B82" s="32" t="s">
+        <v>82</v>
+      </c>
+      <c r="C82" s="32"/>
+      <c r="H82" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="I82" s="1"/>
+      <c r="J82" s="1"/>
+    </row>
+    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B83" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="C83" s="32"/>
+      <c r="H83" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="I83" s="1"/>
+      <c r="J83" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="H77:J77"/>
-    <mergeCell ref="H76:J76"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="H83:J83"/>
+    <mergeCell ref="H82:J82"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="D2:J5"/>
